--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -949,7 +949,7 @@
     <t>0.0114,0.9343,0.2424,0.0037</t>
   </si>
   <si>
-    <t>0.0106,0.0131,0.0913,0.9288</t>
+    <t>0.0106,0.0131,0.0912,0.9288</t>
   </si>
   <si>
     <t>0.0004,0.9849,0.3807,0.0018</t>
@@ -967,7 +967,7 @@
     <t>0.0000,0.9996,0.0001,0.0382</t>
   </si>
   <si>
-    <t>0.0000,0.9995,0.0010,0.0351</t>
+    <t>0.0000,0.9995,0.0010,0.0352</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0004,0.0176</t>
@@ -976,7 +976,7 @@
     <t>0.0005,0.4974,0.9781,0.0006</t>
   </si>
   <si>
-    <t>0.0004,0.7375,0.9583,0.0010</t>
+    <t>0.0004,0.7374,0.9583,0.0010</t>
   </si>
   <si>
     <t>0.0047,0.8697,0.4024,0.0256</t>
@@ -1027,7 +1027,7 @@
     <t>0.0001,0.0315,0.9992,0.0005</t>
   </si>
   <si>
-    <t>0.0000,0.9917,0.0027,0.2975</t>
+    <t>0.0000,0.9917,0.0027,0.2976</t>
   </si>
   <si>
     <t>0.0000,0.9994,0.0002,0.0273</t>
@@ -1357,7 +1357,7 @@
     <t>0.0006,0.0796,0.0002,0.9977</t>
   </si>
   <si>
-    <t>0.0003,0.0227,0.1382,0.8717</t>
+    <t>0.0003,0.0227,0.1381,0.8717</t>
   </si>
   <si>
     <t>0.0004,0.0063,0.0007,0.9991</t>
@@ -1438,7 +1438,7 @@
     <t>0.0014,0.5254,0.0014,0.9723</t>
   </si>
   <si>
-    <t>0.0062,0.6848,0.1849,0.2249</t>
+    <t>0.0062,0.6848,0.1848,0.2249</t>
   </si>
   <si>
     <t>0.0155,0.2339,0.7561,0.0330</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,7 +808,7 @@
     <t>[[0.0, 1.0, 1.0, 0.0]]</t>
   </si>
   <si>
-    <t>1,0,0,0</t>
+    <t>0,0,0,0</t>
   </si>
   <si>
     <t>0,0,0,1</t>
@@ -829,10 +829,10 @@
     <t>0,0,1,1</t>
   </si>
   <si>
-    <t>0.0512,0.3083,0.0625,0.3541</t>
-  </si>
-  <si>
-    <t>0.0001,0.0209,0.0000,0.9998</t>
+    <t>0.0510,0.3090,0.0628,0.3537</t>
+  </si>
+  <si>
+    <t>0.0001,0.0210,0.0000,0.9998</t>
   </si>
   <si>
     <t>0.0052,0.0221,0.0014,0.9948</t>
@@ -847,340 +847,343 @@
     <t>0.0002,0.0021,0.0000,0.9999</t>
   </si>
   <si>
+    <t>0.0001,0.0003,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0254,0.0006,0.9971</t>
+  </si>
+  <si>
+    <t>0.0003,0.0130,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0008,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0147,0.6486,0.0108,0.5951</t>
+  </si>
+  <si>
+    <t>0.0006,0.9533,0.0165,0.3534</t>
+  </si>
+  <si>
+    <t>0.0269,0.8762,0.3205,0.0107</t>
+  </si>
+  <si>
+    <t>0.0040,0.9464,0.6102,0.0038</t>
+  </si>
+  <si>
+    <t>0.0033,0.1319,0.0020,0.9812</t>
+  </si>
+  <si>
+    <t>0.0000,0.9966,0.0004,0.4609</t>
+  </si>
+  <si>
+    <t>0.0000,0.9779,0.0000,0.9869</t>
+  </si>
+  <si>
+    <t>0.0000,0.9908,0.0046,0.3705</t>
+  </si>
+  <si>
+    <t>0.0000,0.8694,0.0000,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.0058,0.0367</t>
+  </si>
+  <si>
+    <t>0.0207,0.2359,0.0085,0.8422</t>
+  </si>
+  <si>
+    <t>0.0018,0.9166,0.0143,0.4771</t>
+  </si>
+  <si>
+    <t>0.0554,0.2914,0.7034,0.0148</t>
+  </si>
+  <si>
+    <t>0.0058,0.9143,0.1739,0.0485</t>
+  </si>
+  <si>
+    <t>0.0051,0.3994,0.0588,0.7094</t>
+  </si>
+  <si>
+    <t>0.0720,0.4749,0.4887,0.0150</t>
+  </si>
+  <si>
+    <t>0.0244,0.2417,0.8188,0.0140</t>
+  </si>
+  <si>
+    <t>0.0002,0.7002,0.0004,0.9873</t>
+  </si>
+  <si>
+    <t>0.0011,0.3579,0.0391,0.8784</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.6952,0.5908</t>
+  </si>
+  <si>
+    <t>0.0003,0.9099,0.0262,0.4230</t>
+  </si>
+  <si>
+    <t>0.0016,0.0020,0.0036,0.9977</t>
+  </si>
+  <si>
+    <t>0.0006,0.0084,0.0035,0.9976</t>
+  </si>
+  <si>
+    <t>0.0000,0.7885,0.0002,0.9944</t>
+  </si>
+  <si>
+    <t>0.0002,0.7242,0.0026,0.9487</t>
+  </si>
+  <si>
+    <t>0.0006,0.9632,0.8808,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.0994,0.9617,0.0128</t>
+  </si>
+  <si>
+    <t>0.0113,0.9344,0.2428,0.0037</t>
+  </si>
+  <si>
+    <t>0.0106,0.0131,0.0916,0.9286</t>
+  </si>
+  <si>
+    <t>0.0004,0.9849,0.3816,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.9943,0.0067,0.0290</t>
+  </si>
+  <si>
+    <t>0.0022,0.9137,0.8270,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.6136,0.0002,0.9974</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0001,0.0382</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0010,0.0351</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0176</t>
+  </si>
+  <si>
+    <t>0.0004,0.4972,0.9781,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.7374,0.9583,0.0010</t>
+  </si>
+  <si>
+    <t>0.0047,0.8697,0.4029,0.0255</t>
+  </si>
+  <si>
+    <t>0.0389,0.0312,0.3258,0.3317</t>
+  </si>
+  <si>
+    <t>0.0121,0.8148,0.4921,0.0161</t>
+  </si>
+  <si>
+    <t>0.0049,0.9255,0.5353,0.0056</t>
+  </si>
+  <si>
+    <t>0.0005,0.0270,0.0004,0.9986</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0083,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.0013,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0013,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.3101,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8879,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.8607,0.8935,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.9896,0.8968,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0314,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9917,0.0027,0.2972</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.0002,0.0273</t>
+  </si>
+  <si>
+    <t>0.0041,0.0754,0.0015,0.9816</t>
+  </si>
+  <si>
+    <t>0.0007,0.8816,0.0103,0.6343</t>
+  </si>
+  <si>
+    <t>0.0021,0.4650,0.0794,0.5637</t>
+  </si>
+  <si>
+    <t>0.0002,0.9961,0.7644,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9952,0.8578,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9978,0.6620,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0855,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.0069,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0018,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0021,0.0006,0.9996</t>
+  </si>
+  <si>
+    <t>0.0005,0.1039,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0003,0.0089,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.4649,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9920,0.7801,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9963,0.1912,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.9952,0.7083,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.7647,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.0777,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0092,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.0151,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0049,0.0213,0.0041,0.9756</t>
+  </si>
+  <si>
+    <t>0.0007,0.0268,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.0023,0.0074,0.9892</t>
+  </si>
+  <si>
+    <t>0.0000,0.0019,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0172,0.0018,0.8687,0.2790</t>
+  </si>
+  <si>
+    <t>0.0002,0.0018,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0065,0.0048,0.0020,0.9856</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0021,0.0040,0.0006,0.9973</t>
+  </si>
+  <si>
+    <t>0.0005,0.0067,0.0002,0.9994</t>
+  </si>
+  <si>
+    <t>0.0120,0.0017,0.0364,0.9608</t>
+  </si>
+  <si>
+    <t>0.0007,0.0130,0.0001,0.9992</t>
+  </si>
+  <si>
     <t>0.0001,0.0003,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0253,0.0006,0.9971</t>
-  </si>
-  <si>
-    <t>0.0003,0.0130,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0147,0.6478,0.0107,0.5954</t>
-  </si>
-  <si>
-    <t>0.0006,0.9532,0.0164,0.3544</t>
-  </si>
-  <si>
-    <t>0.0269,0.8761,0.3200,0.0107</t>
-  </si>
-  <si>
-    <t>0.0040,0.9464,0.6093,0.0039</t>
-  </si>
-  <si>
-    <t>0.0033,0.1316,0.0019,0.9812</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.0004,0.4614</t>
-  </si>
-  <si>
-    <t>0.0000,0.9779,0.0000,0.9869</t>
-  </si>
-  <si>
-    <t>0.0000,0.9908,0.0046,0.3711</t>
-  </si>
-  <si>
-    <t>0.0000,0.8693,0.0000,0.9983</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.0058,0.0368</t>
-  </si>
-  <si>
-    <t>0.0207,0.2354,0.0085,0.8422</t>
-  </si>
-  <si>
-    <t>0.0018,0.9165,0.0142,0.4779</t>
-  </si>
-  <si>
-    <t>0.0556,0.2914,0.7027,0.0149</t>
-  </si>
-  <si>
-    <t>0.0058,0.9142,0.1736,0.0487</t>
-  </si>
-  <si>
-    <t>0.0051,0.3990,0.0586,0.7105</t>
-  </si>
-  <si>
-    <t>0.0722,0.4745,0.4879,0.0151</t>
-  </si>
-  <si>
-    <t>0.0245,0.2415,0.8185,0.0140</t>
-  </si>
-  <si>
-    <t>0.0002,0.6997,0.0004,0.9873</t>
-  </si>
-  <si>
-    <t>0.0011,0.3577,0.0389,0.8787</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.6947,0.5917</t>
-  </si>
-  <si>
-    <t>0.0003,0.9097,0.0261,0.4237</t>
-  </si>
-  <si>
-    <t>0.0016,0.0020,0.0036,0.9977</t>
-  </si>
-  <si>
-    <t>0.0006,0.0084,0.0035,0.9976</t>
-  </si>
-  <si>
-    <t>0.0000,0.7882,0.0002,0.9944</t>
-  </si>
-  <si>
-    <t>0.0002,0.7238,0.0026,0.9488</t>
-  </si>
-  <si>
-    <t>0.0006,0.9633,0.8805,0.0001</t>
-  </si>
-  <si>
-    <t>0.0053,0.0994,0.9616,0.0128</t>
-  </si>
-  <si>
-    <t>0.0114,0.9343,0.2424,0.0037</t>
-  </si>
-  <si>
-    <t>0.0106,0.0131,0.0912,0.9288</t>
-  </si>
-  <si>
-    <t>0.0004,0.9849,0.3807,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.9943,0.0067,0.0289</t>
-  </si>
-  <si>
-    <t>0.0022,0.9137,0.8267,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.6133,0.0002,0.9974</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0001,0.0382</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0010,0.0352</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0176</t>
-  </si>
-  <si>
-    <t>0.0005,0.4974,0.9781,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.7374,0.9583,0.0010</t>
-  </si>
-  <si>
-    <t>0.0047,0.8697,0.4024,0.0256</t>
-  </si>
-  <si>
-    <t>0.0390,0.0311,0.3246,0.3328</t>
-  </si>
-  <si>
-    <t>0.0122,0.8147,0.4911,0.0161</t>
-  </si>
-  <si>
-    <t>0.0049,0.9255,0.5346,0.0056</t>
-  </si>
-  <si>
-    <t>0.0005,0.0269,0.0004,0.9986</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0083,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.0013,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0013,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.3097,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8880,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.8608,0.8933,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.9897,0.8966,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0315,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9917,0.0027,0.2976</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0002,0.0273</t>
-  </si>
-  <si>
-    <t>0.0041,0.0752,0.0015,0.9816</t>
-  </si>
-  <si>
-    <t>0.0007,0.8814,0.0102,0.6349</t>
-  </si>
-  <si>
-    <t>0.0021,0.4647,0.0792,0.5647</t>
-  </si>
-  <si>
-    <t>0.0002,0.9961,0.7641,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9952,0.8575,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0914,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9978,0.6616,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0853,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.0001,0.0068,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0018,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0021,0.0006,0.9996</t>
-  </si>
-  <si>
-    <t>0.0005,0.1037,0.0001,0.9986</t>
-  </si>
-  <si>
-    <t>0.0003,0.0089,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.4642,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9920,0.7798,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9963,0.1908,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9952,0.7079,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.7643,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.0776,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0092,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.0001,0.0151,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0049,0.0213,0.0041,0.9757</t>
-  </si>
-  <si>
-    <t>0.0007,0.0267,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0022,0.0074,0.9892</t>
-  </si>
-  <si>
-    <t>0.0000,0.0019,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0172,0.0018,0.8683,0.2794</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0065,0.0048,0.0020,0.9856</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0021,0.0039,0.0006,0.9973</t>
-  </si>
-  <si>
-    <t>0.0005,0.0067,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0120,0.0017,0.0363,0.9608</t>
-  </si>
-  <si>
-    <t>0.0007,0.0130,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0078,0.0719,0.9317,0.0104</t>
-  </si>
-  <si>
-    <t>0.0038,0.3169,0.0431,0.8159</t>
-  </si>
-  <si>
-    <t>0.1482,0.2877,0.0131,0.2013</t>
-  </si>
-  <si>
-    <t>0.0209,0.8186,0.2461,0.0419</t>
-  </si>
-  <si>
-    <t>0.0000,0.9838,0.0000,0.9965</t>
+    <t>0.0077,0.0719,0.9319,0.0103</t>
+  </si>
+  <si>
+    <t>0.0037,0.3173,0.0432,0.8154</t>
+  </si>
+  <si>
+    <t>0.1478,0.2885,0.0132,0.2014</t>
+  </si>
+  <si>
+    <t>0.0209,0.8188,0.2465,0.0418</t>
+  </si>
+  <si>
+    <t>0.0000,0.9839,0.0000,0.9965</t>
   </si>
   <si>
     <t>0.0000,0.9977,0.0000,0.9669</t>
   </si>
   <si>
-    <t>0.0001,0.9600,0.0013,0.7525</t>
-  </si>
-  <si>
-    <t>0.0001,0.9356,0.0003,0.9462</t>
+    <t>0.0001,0.9601,0.0013,0.7520</t>
+  </si>
+  <si>
+    <t>0.0001,0.9357,0.0003,0.9461</t>
   </si>
   <si>
     <t>0.0000,0.9831,0.0000,0.9978</t>
   </si>
   <si>
-    <t>0.0000,0.9996,0.0000,0.7803</t>
-  </si>
-  <si>
-    <t>0.0002,0.6894,0.0003,0.9786</t>
-  </si>
-  <si>
-    <t>0.0007,0.8303,0.0036,0.8621</t>
-  </si>
-  <si>
-    <t>0.0087,0.9105,0.5365,0.0077</t>
-  </si>
-  <si>
-    <t>0.0019,0.9354,0.0082,0.4057</t>
-  </si>
-  <si>
-    <t>0.0018,0.8345,0.0079,0.7083</t>
-  </si>
-  <si>
-    <t>0.0001,0.8692,0.2400,0.2264</t>
+    <t>0.0000,0.9996,0.0000,0.7799</t>
+  </si>
+  <si>
+    <t>0.0002,0.6898,0.0003,0.9786</t>
+  </si>
+  <si>
+    <t>0.0007,0.8305,0.0036,0.8618</t>
+  </si>
+  <si>
+    <t>0.0087,0.9106,0.5372,0.0077</t>
+  </si>
+  <si>
+    <t>0.0019,0.9355,0.0082,0.4050</t>
+  </si>
+  <si>
+    <t>0.0018,0.8347,0.0080,0.7077</t>
+  </si>
+  <si>
+    <t>0.0001,0.8692,0.2405,0.2258</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0002,0.0149</t>
@@ -1195,28 +1198,28 @@
     <t>0.0000,0.9998,0.0017,0.0082</t>
   </si>
   <si>
-    <t>0.0000,0.9753,0.0021,0.7897</t>
-  </si>
-  <si>
-    <t>0.0001,0.3733,0.0005,0.9957</t>
-  </si>
-  <si>
-    <t>0.0000,0.4676,0.0001,0.9987</t>
+    <t>0.0000,0.9753,0.0021,0.7893</t>
+  </si>
+  <si>
+    <t>0.0001,0.3738,0.0005,0.9957</t>
+  </si>
+  <si>
+    <t>0.0000,0.4680,0.0001,0.9987</t>
   </si>
   <si>
     <t>0.0050,0.0010,0.0001,0.9990</t>
   </si>
   <si>
-    <t>0.0005,0.0288,0.0002,0.9986</t>
-  </si>
-  <si>
-    <t>0.0011,0.0221,0.0002,0.9980</t>
-  </si>
-  <si>
-    <t>0.0003,0.0165,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0361,0.0188,0.0478,0.7720</t>
+    <t>0.0005,0.0289,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.0011,0.0222,0.0002,0.9980</t>
+  </si>
+  <si>
+    <t>0.0003,0.0166,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0360,0.0188,0.0480,0.7716</t>
   </si>
   <si>
     <t>0.0008,0.0024,0.0001,0.9997</t>
@@ -1225,28 +1228,28 @@
     <t>0.0001,0.0002,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0011,0.9856,0.6523,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9896,0.9722,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8922,0.9894,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.9708,0.7323,0.0004</t>
-  </si>
-  <si>
-    <t>0.0034,0.1717,0.0006,0.9873</t>
-  </si>
-  <si>
-    <t>0.0006,0.8884,0.0012,0.9014</t>
-  </si>
-  <si>
-    <t>0.0272,0.5193,0.2740,0.1458</t>
-  </si>
-  <si>
-    <t>0.0027,0.7978,0.0035,0.7951</t>
+    <t>0.0011,0.9856,0.6531,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9895,0.9723,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8921,0.9894,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.9708,0.7328,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.1722,0.0006,0.9872</t>
+  </si>
+  <si>
+    <t>0.0006,0.8885,0.0012,0.9012</t>
+  </si>
+  <si>
+    <t>0.0272,0.5198,0.2747,0.1454</t>
+  </si>
+  <si>
+    <t>0.0027,0.7982,0.0035,0.7948</t>
   </si>
   <si>
     <t>0.0008,0.0013,0.0003,0.9997</t>
@@ -1261,28 +1264,28 @@
     <t>0.0006,0.0180,0.0001,0.9996</t>
   </si>
   <si>
-    <t>0.0002,0.9940,0.7528,0.0001</t>
+    <t>0.0002,0.9940,0.7533,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.0016,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.5466,0.0001,0.9991</t>
+    <t>0.0000,0.5468,0.0001,0.9991</t>
   </si>
   <si>
     <t>0.0002,0.0012,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.3486,0.0001,0.9993</t>
+    <t>0.0000,0.3489,0.0001,0.9993</t>
   </si>
   <si>
     <t>0.0014,0.0129,0.0002,0.9984</t>
   </si>
   <si>
-    <t>0.0764,0.0000,0.9314,0.0000</t>
-  </si>
-  <si>
-    <t>0.0894,0.0000,0.8966,0.0000</t>
+    <t>0.0761,0.0000,0.9317,0.0000</t>
+  </si>
+  <si>
+    <t>0.0892,0.0000,0.8969,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
@@ -1294,28 +1297,28 @@
     <t>0.0002,0.0007,0.0003,0.9998</t>
   </si>
   <si>
-    <t>0.0004,0.0532,0.0010,0.9984</t>
-  </si>
-  <si>
-    <t>0.0017,0.0454,0.0002,0.9972</t>
-  </si>
-  <si>
-    <t>0.0004,0.1637,0.0002,0.9981</t>
-  </si>
-  <si>
-    <t>0.0003,0.9316,0.0029,0.7929</t>
-  </si>
-  <si>
-    <t>0.0031,0.2765,0.0028,0.9593</t>
-  </si>
-  <si>
-    <t>0.0018,0.7488,0.0052,0.7840</t>
+    <t>0.0004,0.0533,0.0010,0.9984</t>
+  </si>
+  <si>
+    <t>0.0017,0.0455,0.0002,0.9972</t>
+  </si>
+  <si>
+    <t>0.0004,0.1642,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0003,0.9317,0.0029,0.7924</t>
+  </si>
+  <si>
+    <t>0.0031,0.2772,0.0028,0.9592</t>
+  </si>
+  <si>
+    <t>0.0018,0.7493,0.0052,0.7836</t>
   </si>
   <si>
     <t>0.0015,0.0136,0.0005,0.9971</t>
   </si>
   <si>
-    <t>0.0027,0.0041,0.0061,0.9928</t>
+    <t>0.0027,0.0041,0.0062,0.9927</t>
   </si>
   <si>
     <t>0.0002,0.0036,0.0000,0.9999</t>
@@ -1324,19 +1327,19 @@
     <t>0.0006,0.0081,0.0002,0.9992</t>
   </si>
   <si>
-    <t>0.0014,0.0352,0.0005,0.9958</t>
-  </si>
-  <si>
-    <t>0.0008,0.0079,0.0002,0.9991</t>
+    <t>0.0014,0.0353,0.0005,0.9958</t>
+  </si>
+  <si>
+    <t>0.0008,0.0080,0.0002,0.9991</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.0003,0.6427,0.0006,0.9834</t>
-  </si>
-  <si>
-    <t>0.0000,0.6011,0.0001,0.9975</t>
+    <t>0.0003,0.6431,0.0006,0.9834</t>
+  </si>
+  <si>
+    <t>0.0000,0.6014,0.0001,0.9975</t>
   </si>
   <si>
     <t>0.0000,0.0171,0.0000,0.9999</t>
@@ -1354,115 +1357,115 @@
     <t>0.0001,0.0004,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0796,0.0002,0.9977</t>
-  </si>
-  <si>
-    <t>0.0003,0.0227,0.1381,0.8717</t>
+    <t>0.0006,0.0798,0.0002,0.9977</t>
+  </si>
+  <si>
+    <t>0.0003,0.0227,0.1385,0.8714</t>
   </si>
   <si>
     <t>0.0004,0.0063,0.0007,0.9991</t>
   </si>
   <si>
-    <t>0.0013,0.2250,0.9871,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.7400,0.7770,0.0105</t>
+    <t>0.0013,0.2249,0.9871,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.7399,0.7777,0.0105</t>
   </si>
   <si>
     <t>0.0011,0.0752,0.0165,0.9809</t>
   </si>
   <si>
-    <t>0.0022,0.9129,0.8751,0.0006</t>
-  </si>
-  <si>
-    <t>0.0024,0.2154,0.9451,0.0056</t>
-  </si>
-  <si>
-    <t>0.0090,0.0462,0.9763,0.0009</t>
-  </si>
-  <si>
-    <t>0.0047,0.5809,0.3579,0.1220</t>
-  </si>
-  <si>
-    <t>0.0030,0.9552,0.0912,0.0706</t>
-  </si>
-  <si>
-    <t>0.0313,0.8275,0.3903,0.0109</t>
-  </si>
-  <si>
-    <t>0.0009,0.9540,0.0024,0.5580</t>
-  </si>
-  <si>
-    <t>0.0010,0.9456,0.0129,0.4359</t>
-  </si>
-  <si>
-    <t>0.0006,0.9698,0.0341,0.1302</t>
-  </si>
-  <si>
-    <t>0.0117,0.8880,0.3899,0.0203</t>
-  </si>
-  <si>
-    <t>0.0035,0.8897,0.0203,0.3704</t>
-  </si>
-  <si>
-    <t>0.0032,0.9720,0.2170,0.0109</t>
-  </si>
-  <si>
-    <t>0.0004,0.3807,0.0307,0.8688</t>
-  </si>
-  <si>
-    <t>0.0000,0.7115,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0000,0.3000,0.0001,0.9991</t>
+    <t>0.0022,0.9129,0.8754,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.2153,0.9454,0.0056</t>
+  </si>
+  <si>
+    <t>0.0090,0.0462,0.9764,0.0009</t>
+  </si>
+  <si>
+    <t>0.0047,0.5812,0.3590,0.1215</t>
+  </si>
+  <si>
+    <t>0.0030,0.9552,0.0914,0.0703</t>
+  </si>
+  <si>
+    <t>0.0312,0.8278,0.3908,0.0109</t>
+  </si>
+  <si>
+    <t>0.0009,0.9540,0.0024,0.5575</t>
+  </si>
+  <si>
+    <t>0.0010,0.9456,0.0129,0.4351</t>
+  </si>
+  <si>
+    <t>0.0006,0.9699,0.0342,0.1297</t>
+  </si>
+  <si>
+    <t>0.0117,0.8882,0.3905,0.0202</t>
+  </si>
+  <si>
+    <t>0.0035,0.8898,0.0204,0.3697</t>
+  </si>
+  <si>
+    <t>0.0032,0.9720,0.2176,0.0109</t>
+  </si>
+  <si>
+    <t>0.0004,0.3810,0.0308,0.8686</t>
+  </si>
+  <si>
+    <t>0.0000,0.7119,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.0000,0.3004,0.0001,0.9991</t>
   </si>
   <si>
     <t>0.0000,0.0010,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0520,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.9818,0.0009,0.4882</t>
-  </si>
-  <si>
-    <t>0.0038,0.1568,0.0003,0.9848</t>
-  </si>
-  <si>
-    <t>0.0024,0.9140,0.0141,0.4694</t>
-  </si>
-  <si>
-    <t>0.0180,0.8141,0.2771,0.0655</t>
-  </si>
-  <si>
-    <t>0.0014,0.5254,0.0014,0.9723</t>
-  </si>
-  <si>
-    <t>0.0062,0.6848,0.1848,0.2249</t>
-  </si>
-  <si>
-    <t>0.0155,0.2339,0.7561,0.0330</t>
-  </si>
-  <si>
-    <t>0.0115,0.9103,0.3574,0.0075</t>
-  </si>
-  <si>
-    <t>0.0092,0.8881,0.6249,0.0020</t>
-  </si>
-  <si>
-    <t>0.0068,0.8375,0.6790,0.0015</t>
+    <t>0.0000,0.0521,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.9818,0.0009,0.4878</t>
+  </si>
+  <si>
+    <t>0.0037,0.1574,0.0003,0.9848</t>
+  </si>
+  <si>
+    <t>0.0024,0.9141,0.0142,0.4685</t>
+  </si>
+  <si>
+    <t>0.0180,0.8143,0.2777,0.0652</t>
+  </si>
+  <si>
+    <t>0.0014,0.5259,0.0014,0.9722</t>
+  </si>
+  <si>
+    <t>0.0062,0.6851,0.1854,0.2240</t>
+  </si>
+  <si>
+    <t>0.0155,0.2335,0.7569,0.0329</t>
+  </si>
+  <si>
+    <t>0.0114,0.9102,0.3581,0.0075</t>
+  </si>
+  <si>
+    <t>0.0092,0.8880,0.6255,0.0020</t>
+  </si>
+  <si>
+    <t>0.0068,0.8373,0.6796,0.0015</t>
   </si>
   <si>
     <t>0.0001,0.0105,0.0001,0.9998</t>
   </si>
   <si>
-    <t>0.0002,0.0574,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0017,0.0198,0.0012,0.9954</t>
-  </si>
-  <si>
-    <t>0.0004,0.0329,0.0001,0.9990</t>
+    <t>0.0002,0.0575,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0017,0.0199,0.0012,0.9954</t>
+  </si>
+  <si>
+    <t>0.0004,0.0330,0.0001,0.9990</t>
   </si>
   <si>
     <t>0.0002,0.0191,0.0000,0.9996</t>
@@ -1471,64 +1474,64 @@
     <t>0.0001,0.0049,0.0000,0.9998</t>
   </si>
   <si>
-    <t>0.0005,0.0259,0.0177,0.9785</t>
-  </si>
-  <si>
-    <t>0.0002,0.3772,0.0014,0.9934</t>
-  </si>
-  <si>
-    <t>0.0002,0.3049,0.0007,0.9957</t>
-  </si>
-  <si>
-    <t>0.0006,0.1961,0.9943,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.2642,0.9923,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.8902,0.7098,0.0060</t>
-  </si>
-  <si>
-    <t>0.0001,0.0179,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0045,0.9642,0.3628,0.0043</t>
+    <t>0.0005,0.0259,0.0178,0.9784</t>
+  </si>
+  <si>
+    <t>0.0002,0.3775,0.0014,0.9934</t>
+  </si>
+  <si>
+    <t>0.0002,0.3053,0.0007,0.9957</t>
+  </si>
+  <si>
+    <t>0.0006,0.1958,0.9943,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.2641,0.9923,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.8902,0.7105,0.0060</t>
+  </si>
+  <si>
+    <t>0.0001,0.0178,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.9642,0.3632,0.0042</t>
   </si>
   <si>
     <t>0.0000,0.0013,0.9997,0.0000</t>
   </si>
   <si>
-    <t>0.0041,0.8935,0.8582,0.0010</t>
-  </si>
-  <si>
-    <t>0.0012,0.9673,0.0236,0.1742</t>
-  </si>
-  <si>
-    <t>0.0282,0.6680,0.0089,0.2915</t>
-  </si>
-  <si>
-    <t>0.0159,0.2122,0.0026,0.9213</t>
-  </si>
-  <si>
-    <t>0.0038,0.5831,0.0002,0.8921</t>
+    <t>0.0041,0.8935,0.8584,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.9673,0.0237,0.1737</t>
+  </si>
+  <si>
+    <t>0.0282,0.6687,0.0089,0.2914</t>
+  </si>
+  <si>
+    <t>0.0159,0.2128,0.0026,0.9212</t>
+  </si>
+  <si>
+    <t>0.0038,0.5839,0.0002,0.8923</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0017,0.0386,0.0024,0.9886</t>
+    <t>0.0017,0.0387,0.0024,0.9886</t>
   </si>
   <si>
     <t>0.0001,0.0021,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0001,0.0770,0.0000,0.9997</t>
+    <t>0.0001,0.0772,0.0000,0.9996</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0548,0.0001,0.9994</t>
+    <t>0.0002,0.0549,0.0001,0.9994</t>
   </si>
   <si>
     <t>0.0004,0.0240,0.0001,0.9993</t>
@@ -1537,46 +1540,46 @@
     <t>0.0000,0.0054,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0011,0.9871,0.3994,0.0012</t>
-  </si>
-  <si>
-    <t>0.0014,0.9452,0.9174,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.8954,0.8452,0.0009</t>
-  </si>
-  <si>
-    <t>0.0037,0.9666,0.1408,0.0147</t>
-  </si>
-  <si>
-    <t>0.0274,0.4739,0.8348,0.0037</t>
-  </si>
-  <si>
-    <t>0.0126,0.0211,0.0362,0.9552</t>
-  </si>
-  <si>
-    <t>0.0034,0.1463,0.2078,0.6471</t>
-  </si>
-  <si>
-    <t>0.0037,0.0910,0.9486,0.0268</t>
-  </si>
-  <si>
-    <t>0.0076,0.0057,0.0006,0.9960</t>
-  </si>
-  <si>
-    <t>0.0000,0.0635,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0040,0.0108,0.0011,0.9968</t>
-  </si>
-  <si>
-    <t>0.0003,0.0268,0.0077,0.9982</t>
-  </si>
-  <si>
-    <t>0.0002,0.0126,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0008,0.2129,0.0012,0.9904</t>
+    <t>0.0011,0.9871,0.3998,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.9452,0.9176,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.8954,0.8455,0.0009</t>
+  </si>
+  <si>
+    <t>0.0037,0.9666,0.1411,0.0147</t>
+  </si>
+  <si>
+    <t>0.0273,0.4740,0.8352,0.0037</t>
+  </si>
+  <si>
+    <t>0.0125,0.0211,0.0364,0.9551</t>
+  </si>
+  <si>
+    <t>0.0034,0.1463,0.2085,0.6461</t>
+  </si>
+  <si>
+    <t>0.0036,0.0909,0.9486,0.0268</t>
+  </si>
+  <si>
+    <t>0.0076,0.0057,0.0006,0.9959</t>
+  </si>
+  <si>
+    <t>0.0000,0.0636,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0039,0.0109,0.0011,0.9968</t>
+  </si>
+  <si>
+    <t>0.0003,0.0269,0.0077,0.9982</t>
+  </si>
+  <si>
+    <t>0.0002,0.0127,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0008,0.2133,0.0012,0.9903</t>
   </si>
 </sst>
 </file>
@@ -3390,7 +3393,7 @@
         <v>265</v>
       </c>
       <c r="D104" t="s">
-        <v>277</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3407,7 @@
         <v>269</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3421,7 @@
         <v>265</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3435,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3449,7 @@
         <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3463,7 @@
         <v>266</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3477,7 @@
         <v>266</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3491,7 @@
         <v>266</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3505,7 @@
         <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3519,7 @@
         <v>266</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3533,7 @@
         <v>266</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3547,7 @@
         <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3561,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3575,7 @@
         <v>268</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3586,7 +3589,7 @@
         <v>267</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3600,7 +3603,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3617,7 @@
         <v>267</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3631,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3645,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3659,7 @@
         <v>266</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3673,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3687,7 @@
         <v>266</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,7 +3701,7 @@
         <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3715,7 @@
         <v>265</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3729,7 @@
         <v>265</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3743,7 @@
         <v>265</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3757,7 @@
         <v>265</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3771,7 @@
         <v>265</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3785,7 @@
         <v>265</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3799,7 @@
         <v>265</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3824,7 +3827,7 @@
         <v>265</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3841,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3855,7 @@
         <v>268</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3869,7 @@
         <v>268</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3883,7 @@
         <v>268</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3897,7 @@
         <v>265</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3911,7 @@
         <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3922,7 +3925,7 @@
         <v>267</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3939,7 @@
         <v>266</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3953,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3967,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3981,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3995,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4009,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4023,7 @@
         <v>265</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4037,7 @@
         <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4051,7 @@
         <v>265</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4065,7 @@
         <v>265</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4079,7 @@
         <v>265</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4093,7 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4107,7 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4118,7 +4121,7 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4135,7 @@
         <v>265</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4149,7 @@
         <v>265</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4163,7 @@
         <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4177,7 @@
         <v>265</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4191,7 @@
         <v>265</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,7 +4205,7 @@
         <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4219,7 @@
         <v>265</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4233,7 @@
         <v>266</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4247,7 @@
         <v>265</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4261,7 @@
         <v>265</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4275,7 @@
         <v>265</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4300,7 +4303,7 @@
         <v>265</v>
       </c>
       <c r="D169" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4317,7 @@
         <v>265</v>
       </c>
       <c r="D170" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4331,7 @@
         <v>265</v>
       </c>
       <c r="D171" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4345,7 @@
         <v>265</v>
       </c>
       <c r="D172" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4359,7 @@
         <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,7 +4373,7 @@
         <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4387,7 @@
         <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4398,7 +4401,7 @@
         <v>265</v>
       </c>
       <c r="D176" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4415,7 @@
         <v>265</v>
       </c>
       <c r="D177" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4429,7 @@
         <v>265</v>
       </c>
       <c r="D178" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4443,7 @@
         <v>265</v>
       </c>
       <c r="D179" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4457,7 @@
         <v>265</v>
       </c>
       <c r="D180" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4471,7 @@
         <v>265</v>
       </c>
       <c r="D181" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4485,7 @@
         <v>265</v>
       </c>
       <c r="D182" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4499,7 @@
         <v>269</v>
       </c>
       <c r="D183" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4513,7 @@
         <v>268</v>
       </c>
       <c r="D184" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4527,7 @@
         <v>265</v>
       </c>
       <c r="D185" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4541,7 @@
         <v>268</v>
       </c>
       <c r="D186" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4555,7 @@
         <v>269</v>
       </c>
       <c r="D187" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4569,7 @@
         <v>269</v>
       </c>
       <c r="D188" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4583,7 @@
         <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4597,7 @@
         <v>267</v>
       </c>
       <c r="D190" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4611,7 @@
         <v>267</v>
       </c>
       <c r="D191" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,7 +4625,7 @@
         <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4636,7 +4639,7 @@
         <v>267</v>
       </c>
       <c r="D193" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4650,7 +4653,7 @@
         <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4664,7 +4667,7 @@
         <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4681,7 @@
         <v>267</v>
       </c>
       <c r="D196" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4695,7 @@
         <v>267</v>
       </c>
       <c r="D197" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4706,7 +4709,7 @@
         <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4723,7 @@
         <v>266</v>
       </c>
       <c r="D199" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4737,7 @@
         <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4751,7 @@
         <v>265</v>
       </c>
       <c r="D201" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4765,7 @@
         <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4779,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4793,7 @@
         <v>265</v>
       </c>
       <c r="D204" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4807,7 @@
         <v>267</v>
       </c>
       <c r="D205" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4821,7 @@
         <v>267</v>
       </c>
       <c r="D206" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4832,7 +4835,7 @@
         <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4849,7 @@
         <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4863,7 @@
         <v>269</v>
       </c>
       <c r="D209" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4877,7 @@
         <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4891,7 @@
         <v>268</v>
       </c>
       <c r="D211" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4902,7 +4905,7 @@
         <v>268</v>
       </c>
       <c r="D212" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4930,7 +4933,7 @@
         <v>265</v>
       </c>
       <c r="D214" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4947,7 @@
         <v>265</v>
       </c>
       <c r="D215" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4961,7 @@
         <v>265</v>
       </c>
       <c r="D216" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4975,7 @@
         <v>265</v>
       </c>
       <c r="D217" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4989,7 @@
         <v>265</v>
       </c>
       <c r="D218" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5003,7 @@
         <v>265</v>
       </c>
       <c r="D219" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5028,7 +5031,7 @@
         <v>265</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5045,7 @@
         <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5059,7 @@
         <v>265</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5073,7 @@
         <v>269</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5087,7 @@
         <v>269</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5101,7 @@
         <v>268</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5115,7 @@
         <v>269</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5129,7 @@
         <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5143,7 @@
         <v>269</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5157,7 @@
         <v>268</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5171,7 @@
         <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5185,7 @@
         <v>267</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5199,7 @@
         <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5213,7 @@
         <v>266</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5227,7 @@
         <v>265</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5241,7 @@
         <v>265</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5255,7 @@
         <v>265</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5269,7 @@
         <v>265</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5283,7 @@
         <v>265</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5297,7 @@
         <v>265</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5311,7 @@
         <v>265</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5325,7 @@
         <v>265</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5339,7 @@
         <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5353,7 @@
         <v>268</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5367,7 @@
         <v>268</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5381,7 @@
         <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5395,7 @@
         <v>269</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,7 +5409,7 @@
         <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5423,7 @@
         <v>265</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5434,7 +5437,7 @@
         <v>269</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5451,7 @@
         <v>265</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5465,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5479,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5493,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5507,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5521,7 @@
         <v>265</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
